--- a/src/main/resources/Errors.xlsx
+++ b/src/main/resources/Errors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8061E6F3-56B9-4E7E-A27C-CA8DC7B41273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C3233B-7997-4512-B537-7E14668AF827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="210" yWindow="0" windowWidth="20355" windowHeight="10920" firstSheet="1" activeTab="1" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
   </bookViews>
   <sheets>
     <sheet name="AnnualError" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="31">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -114,9 +114,6 @@
     <t>Construction</t>
   </si>
   <si>
-    <t>fieldInternalOrganization__c</t>
-  </si>
-  <si>
     <t>SAN DIEGO ELECTRICAL TRAINING TRUST</t>
   </si>
   <si>
@@ -132,22 +129,7 @@
     <t>Test Automation Organization</t>
   </si>
   <si>
-    <t>fieldFrequency__c</t>
-  </si>
-  <si>
-    <t>fieldCalReportingStartDate__c</t>
-  </si>
-  <si>
-    <t>fieldCalReportingEndDate__c</t>
-  </si>
-  <si>
-    <t>fieldSubmissionTitle__c</t>
-  </si>
-  <si>
-    <t>fieldScheduleBase__c</t>
-  </si>
-  <si>
-    <t>fieldDescription__c</t>
+    <t>InternalOrganization__c</t>
   </si>
 </sst>
 </file>
@@ -223,9 +205,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -263,7 +245,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -369,7 +351,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -511,7 +493,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -635,7 +617,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -646,7 +628,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
@@ -657,7 +639,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -668,7 +650,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
@@ -679,7 +661,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -690,7 +672,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="C7">
         <v>20</v>
@@ -819,7 +801,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -830,7 +812,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
@@ -841,7 +823,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -852,7 +834,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
@@ -863,7 +845,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -874,7 +856,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1047,10 +1029,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
         <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1058,10 +1040,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
         <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1069,10 +1051,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
         <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1117,7 +1099,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>

--- a/src/main/resources/Errors.xlsx
+++ b/src/main/resources/Errors.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OldLaptopBackup\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C3233B-7997-4512-B537-7E14668AF827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D99E549-D259-4850-8615-2F0470C3968E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="4" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
   </bookViews>
   <sheets>
     <sheet name="AnnualError" sheetId="2" r:id="rId1"/>
